--- a/outputs/51-12.xlsx
+++ b/outputs/51-12.xlsx
@@ -147,31 +147,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/outputs/51-12.xlsx
+++ b/outputs/51-12.xlsx
@@ -29,15 +29,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0%"/>
   </numFmts>
   <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -57,63 +56,20 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.7999"/>
-        <bgColor rgb="FFDEEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999"/>
-        <bgColor rgb="FFFBE5D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999"/>
-        <bgColor rgb="FFE2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999"/>
-        <bgColor rgb="FFDEEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -142,36 +98,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -184,71 +116,11 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFBE5D6"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFDEEBF7"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD6DCE5"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFE2F0D9"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -258,44 +130,44 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -309,63 +181,54 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -383,34 +246,46 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
+                <a:shade val="20000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -425,9 +300,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="n">
         <v>100</v>
       </c>
@@ -437,74 +312,62 @@
       <c r="C1" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="D1" s="2" t="n">
+      <c r="D1" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="E1" s="2" t="n">
+      <c r="E1" s="1" t="n">
         <v>220</v>
       </c>
-      <c r="F1" s="3" t="n">
+      <c r="F1" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="G1" s="3" t="n">
+      <c r="G1" s="1" t="n">
         <v>260</v>
       </c>
-      <c r="H1" s="3" t="n">
+      <c r="H1" s="1" t="n">
         <v>275</v>
       </c>
-      <c r="I1" s="4" t="n">
+      <c r="I1" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="J1" s="4" t="n">
+      <c r="J1" s="1" t="n">
         <v>175</v>
       </c>
-      <c r="K1" s="4" t="n">
+      <c r="K1" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="L1" s="4" t="n">
+      <c r="L1" s="1" t="n">
         <v>177</v>
       </c>
-      <c r="M1" s="5" t="n">
+      <c r="M1" s="1" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="M2" s="5"/>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G4" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>4</v>
+      <c r="B6" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
